--- a/artfynd/A 4669-2024 artfynd.xlsx
+++ b/artfynd/A 4669-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4669-2024 artfynd.xlsx
+++ b/artfynd/A 4669-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3580,6 +3580,117 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120320574</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>694691</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6383725</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
